--- a/매입장부.xlsx
+++ b/매입장부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hwang\Desktop\변환기\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F619EF-05EA-4176-B7C7-BE0203AE04DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CA437A-9B61-4880-B1AB-83B6C25DADAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-17944" yWindow="88" windowWidth="18032" windowHeight="13435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -481,7 +481,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2">
-        <v>74500</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">

--- a/매입장부.xlsx
+++ b/매입장부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hwang\Desktop\변환기\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CA437A-9B61-4880-B1AB-83B6C25DADAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651902A4-CC05-44BA-AD55-FD89EF583AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-17944" yWindow="88" windowWidth="18032" windowHeight="13435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>종목명</t>
   </si>
@@ -34,9 +34,6 @@
     <t>매도일자</t>
   </si>
   <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
     <t>2026-03-15</t>
   </si>
   <si>
@@ -77,6 +74,10 @@
   </si>
   <si>
     <t>삼양식품</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대한광통신</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -142,12 +143,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -452,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="18.2" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -475,98 +479,98 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46099</v>
       </c>
       <c r="C2" s="2">
-        <v>25000</v>
+        <v>25450</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46100</v>
       </c>
       <c r="C3" s="2">
-        <v>180000</v>
+        <v>196100</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46099</v>
       </c>
       <c r="C4" s="2">
-        <v>250000</v>
+        <v>211000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46099</v>
       </c>
       <c r="C5" s="2">
-        <v>230000</v>
+        <v>218000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46099</v>
       </c>
       <c r="C6" s="2">
-        <v>78000</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46097</v>
       </c>
       <c r="C7" s="2">
-        <v>190000</v>
+        <v>190200</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46098</v>
       </c>
       <c r="C8" s="2">
-        <v>65000</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46097</v>
       </c>
       <c r="C9" s="2">
-        <v>26000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="2">
         <v>48000</v>
@@ -574,13 +578,24 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46097</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1091000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1080000</v>
+      <c r="B12" s="3">
+        <v>46098</v>
+      </c>
+      <c r="C12" s="2">
+        <v>7400</v>
       </c>
     </row>
   </sheetData>

--- a/매입장부.xlsx
+++ b/매입장부.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hwang\Desktop\변환기\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651902A4-CC05-44BA-AD55-FD89EF583AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11C3EDC-AF94-4924-8378-3E52A2E6E0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-17944" yWindow="88" windowWidth="18032" windowHeight="13435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,10 +45,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>리가캠바이오</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ISC</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -78,6 +74,10 @@
   </si>
   <si>
     <t>대한광통신</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리가켐바이오</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -501,7 +501,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3">
         <v>46099</v>
@@ -512,7 +512,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3">
         <v>46099</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3">
         <v>46099</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
         <v>46097</v>
@@ -545,7 +545,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3">
         <v>46098</v>
@@ -556,7 +556,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3">
         <v>46097</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>46097</v>
@@ -589,7 +589,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="3">
         <v>46098</v>

--- a/매입장부.xlsx
+++ b/매입장부.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hwang\Desktop\변환기\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFD1086-4A92-4294-A5FF-3759626A22E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D623E67-767C-45DB-8D3C-84C813E29AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23929" yWindow="-113" windowWidth="24267" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26709" yWindow="2780" windowWidth="11921" windowHeight="9842" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="매입장부" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>종목명</t>
   </si>
@@ -31,66 +31,43 @@
     <t>매수단가</t>
   </si>
   <si>
+    <t>대주전자재료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로보티즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리가켐바이오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이피알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이비엘바이오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LS머트리얼즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨어스테크놀로지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오름테라퓨틱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>노타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>매도일자</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>대한항공</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>알지노믹스</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ISC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>한화비전</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>에이비엘바이오</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>에임드바이오</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>제닉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>노타</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>삼양식품</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대한광통신</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>리가켐바이오</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LS머트리얼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>씨어스테크놀로지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>에이유브랜즈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -155,17 +132,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -468,11 +440,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="18.2" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="4" width="11.8984375" style="2" customWidth="1"/>
+    <col min="1" max="3" width="15.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -485,162 +456,107 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="D1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3">
-        <v>46099</v>
-      </c>
-      <c r="C2" s="2">
-        <v>25450</v>
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45377</v>
+      </c>
+      <c r="C2">
+        <v>134800</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46100</v>
-      </c>
-      <c r="C3" s="2">
-        <v>196100</v>
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45377</v>
+      </c>
+      <c r="C3">
+        <v>251500</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46099</v>
-      </c>
-      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45369</v>
+      </c>
+      <c r="C4">
         <v>211000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3">
-        <v>46099</v>
-      </c>
-      <c r="C5" s="2">
-        <v>218000</v>
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45377</v>
+      </c>
+      <c r="C5">
+        <v>320500</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46099</v>
-      </c>
-      <c r="C6" s="2">
-        <v>79300</v>
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45368</v>
+      </c>
+      <c r="C6">
+        <v>191233</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46097</v>
-      </c>
-      <c r="C7" s="2">
-        <v>190200</v>
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45375</v>
+      </c>
+      <c r="C7">
+        <v>23900</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46098</v>
-      </c>
-      <c r="C8" s="2">
-        <v>63800</v>
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45375</v>
+      </c>
+      <c r="C8">
+        <v>63300</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3">
-        <v>46097</v>
-      </c>
-      <c r="C9" s="2">
-        <v>28000</v>
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45377</v>
+      </c>
+      <c r="C9">
+        <v>119300</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3">
-        <v>46097</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1091000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>46098</v>
-      </c>
-      <c r="C12" s="2">
-        <v>7400</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="3">
-        <v>46105</v>
-      </c>
-      <c r="C13" s="2">
-        <v>23900</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="3">
-        <v>46105</v>
-      </c>
-      <c r="C14" s="2">
-        <v>63300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="3">
-        <v>46097</v>
-      </c>
-      <c r="C15" s="2">
-        <v>19281</v>
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45367</v>
+      </c>
+      <c r="C10">
+        <v>47033</v>
       </c>
     </row>
   </sheetData>

--- a/매입장부.xlsx
+++ b/매입장부.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hwang\Desktop\변환기\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D623E67-767C-45DB-8D3C-84C813E29AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75ADFF6-7791-47C3-AF04-6A6233E7FFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26709" yWindow="2780" windowWidth="11921" windowHeight="9842" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="751" yWindow="751" windowWidth="18032" windowHeight="9842" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매입장부" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>종목명</t>
   </si>
@@ -68,6 +68,38 @@
   </si>
   <si>
     <t>매도일자</t>
+  </si>
+  <si>
+    <t>테스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lg에너지솔루션</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이유브랜즈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>time코스닥액티브</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kctc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼성에피스홀딩스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼성전자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>세아제강지주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -440,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="18.2" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="3" width="15.3984375" customWidth="1"/>
@@ -465,7 +497,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>45377</v>
+        <v>46107</v>
       </c>
       <c r="C2">
         <v>134800</v>
@@ -476,7 +508,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45377</v>
+        <v>46107</v>
       </c>
       <c r="C3">
         <v>251500</v>
@@ -487,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>45369</v>
+        <v>46099</v>
       </c>
       <c r="C4">
         <v>211000</v>
@@ -498,7 +530,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>45377</v>
+        <v>46107</v>
       </c>
       <c r="C5">
         <v>320500</v>
@@ -509,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2">
-        <v>45368</v>
+        <v>46098</v>
       </c>
       <c r="C6">
         <v>191233</v>
@@ -520,7 +552,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2">
-        <v>45375</v>
+        <v>46105</v>
       </c>
       <c r="C7">
         <v>23900</v>
@@ -531,7 +563,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>45375</v>
+        <v>46105</v>
       </c>
       <c r="C8">
         <v>63300</v>
@@ -542,7 +574,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2">
-        <v>45377</v>
+        <v>46107</v>
       </c>
       <c r="C9">
         <v>119300</v>
@@ -553,10 +585,98 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>45367</v>
+        <v>46097</v>
       </c>
       <c r="C10">
         <v>47033</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C11">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C12">
+        <v>407000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C13">
+        <v>19281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C14">
+        <v>12498</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C15">
+        <v>8140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C16">
+        <v>746000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C17">
+        <v>200125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C18">
+        <v>233000</v>
       </c>
     </row>
   </sheetData>
